--- a/Mosfet_extraction_pipeline/High_side_frequency_optimization_matrix.xlsx
+++ b/Mosfet_extraction_pipeline/High_side_frequency_optimization_matrix.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Sync_Buck_convertor\Mosfet_extraction_pipeline\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4365EEA1-7ABC-446F-9A18-151C21A6E406}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A503EE73-8468-4FCF-9C53-4B0876B9B743}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -106,12 +106,18 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -141,11 +147,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2516,32 +2523,32 @@
         <v>3.5897435897435899</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A72">
+    <row r="72" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A72" s="2">
         <v>450</v>
       </c>
-      <c r="B72">
+      <c r="B72" s="2">
         <v>1</v>
       </c>
-      <c r="C72" t="s">
+      <c r="C72" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D72">
+      <c r="D72" s="2">
         <v>0.1688156190476191</v>
       </c>
-      <c r="E72">
+      <c r="E72" s="2">
         <v>4.2750000000000003E-2</v>
       </c>
-      <c r="F72">
+      <c r="F72" s="2">
         <v>9.1999999999999993</v>
       </c>
-      <c r="G72">
+      <c r="G72" s="2">
         <v>1.8</v>
       </c>
-      <c r="H72">
+      <c r="H72" s="2">
         <v>9.5</v>
       </c>
-      <c r="I72">
+      <c r="I72" s="2">
         <v>5.28</v>
       </c>
     </row>
